--- a/report_forms/044_software_project_outcome_report_form--report_forms.xlsx
+++ b/report_forms/044_software_project_outcome_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1178,8 +1178,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_members'}</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team Members'}</t>
+          <t>Team Members</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'external_contractors'}</t>
+          <t>external_contractors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'External Contractors'}</t>
+          <t>External Contractors</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'project_sponsor'}</t>
+          <t>project_sponsor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Project Sponsor'}</t>
+          <t>Project Sponsor</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'customers'}</t>
+          <t>customers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Customers'}</t>
+          <t>Customers</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
